--- a/etf_holdings/2026-10-08_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00400A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2585</t>
+          <t>-1.35%2550</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.35%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2585</v>
+        <v>2550</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.58%1,034,000</t>
+          <t>8.63%1,034,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.58%</t>
+          <t>8.63%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.73%4835</t>
+          <t>-3%4690</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.73%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4835</v>
+        <v>4690</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.41%413,000</t>
+          <t>6.34%413,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.41%</t>
+          <t>6.34%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.75%5950</t>
+          <t>+0.84%6000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.75%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5950</v>
+        <v>6000</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.39%282,000</t>
+          <t>5.54%282,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>5.54%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.38%1305</t>
+          <t>-2.68%1270</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1305</v>
+        <v>1270</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.07%1,209,000</t>
+          <t>5.03%1,209,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.07%</t>
+          <t>5.03%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.88%6805</t>
+          <t>-1.26%1965</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.88%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6805</v>
+        <v>1965</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.83%221,000</t>
+          <t>4.30%669,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.83%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>221000</v>
+        <v>669000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-10%11790</t>
+          <t>-2.96%3440</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>11790</v>
+        <v>3440</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.66%123,000</t>
+          <t>4.25%377,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.66%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>123000</v>
+        <v>377000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.8%3545</t>
+          <t>-1.27%310</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3545</v>
+        <v>310</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.29%377,000</t>
+          <t>4.23%4,167,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.29%</t>
+          <t>4.23%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>377000</v>
+        <v>4167000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.93%1990</t>
+          <t>+5.29%7165</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1990</v>
+        <v>7165</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.27%669,000</t>
+          <t>4.13%176,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.13%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>669000</v>
+        <v>176000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+7.17%314</t>
+          <t>-1.18%8360</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+7.17%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>314</v>
+        <v>8360</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.20%4,167,000</t>
+          <t>3.75%137,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>4167000</v>
+        <v>137000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.01%8460</t>
+          <t>-2.92%2330</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-2.92%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>8460</v>
+        <v>2330</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.72%137,000</t>
+          <t>3.58%470,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>137000</v>
+        <v>470000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.13%2400</t>
+          <t>+0.81%5575</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.13%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2400</v>
+        <v>5575</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.62%470,000</t>
+          <t>3.30%181,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.62%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>470000</v>
+        <v>181000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.83%1215</t>
+          <t>-7%1130</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.83%</t>
+          <t>-7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1215</v>
+        <v>1130</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.45%884,000</t>
+          <t>3.27%884,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.27%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,25 +1236,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.47%5530</t>
+          <t>0%2240</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5530</v>
+        <v>2240</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.21%181,000</t>
+          <t>3.21%438,197</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1263,11 +1263,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>181000</v>
+        <v>438197</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.18%2240</t>
+          <t>-0.65%1525</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2240</v>
+        <v>1525</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.15%438,197</t>
+          <t>2.98%596,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>438197</v>
+        <v>596000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:40</t>
+          <t>2026-10-08 23:49:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0%1535</t>
+          <t>-9.97%10615</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-9.97%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1535</v>
+        <v>10615</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.94%596,000</t>
+          <t>2.71%78,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>596000</v>
+        <v>78000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.51%17750</t>
+          <t>+3.7%4345</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.51%</t>
+          <t>+3.7%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>17750</v>
+        <v>4345</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.70%47,400</t>
+          <t>2.62%184,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.62%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>47400</v>
+        <v>184000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6505台塑化</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.43%2315</t>
+          <t>+3.27%110.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+3.27%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2315</v>
+        <v>110.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.19%295,000</t>
+          <t>2.22%6,147,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.22%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>295000</v>
+        <v>6147000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>6505台塑化</t>
+          <t>3044健鼎</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+5.42%107</t>
+          <t>0%582</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+5.42%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>107</v>
+        <v>582</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.11%6,147,000</t>
+          <t>1.97%1,034,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>6147000</v>
+        <v>1034000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3044健鼎</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.52%582</t>
+          <t>+1.94%2360</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+1.94%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>582</v>
+        <v>2360</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.93%1,034,000</t>
+          <t>1.76%228,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.76%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1034000</v>
+        <v>228000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.65%155.5</t>
+          <t>-1.49%17485</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>155.5</v>
+        <v>17485</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.55%3,104,000</t>
+          <t>1.63%28,400</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>3104000</v>
+        <v>28400</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.23%215.5</t>
+          <t>+3.21%1285</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+3.21%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>215.5</v>
+        <v>1285</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.53%2,208,000</t>
+          <t>1.59%378,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>2208000</v>
+        <v>378000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.19%1245</t>
+          <t>0%215.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1245</v>
+        <v>215.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.51%378,000</t>
+          <t>1.56%2,208,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>378000</v>
+        <v>2208000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-3.21%3015</t>
+          <t>-1.61%153</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-3.21%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3015</v>
+        <v>153</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.28%132,000</t>
+          <t>1.55%3,104,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>132000</v>
+        <v>3104000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-1.61%732</t>
+          <t>-3.32%2915</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-1.61%</t>
+          <t>-3.32%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>732</v>
+        <v>2915</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.09%464,000</t>
+          <t>1.26%132,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>464000</v>
+        <v>132000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.68%148.5</t>
+          <t>+1.64%744</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>148.5</v>
+        <v>744</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.00%2,096,000</t>
+          <t>1.13%464,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2096000</v>
+        <v>464000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.5%299.5</t>
+          <t>-0.67%147.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-0.67%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>299.5</v>
+        <v>147.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.96%999,000</t>
+          <t>1.01%2,096,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>999000</v>
+        <v>2096000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-2.38%246</t>
+          <t>+1.67%304.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>246</v>
+        <v>304.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.87%1,107,336</t>
+          <t>1.00%999,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1107336</v>
+        <v>999000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.69%232.5</t>
+          <t>+0.81%248</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>+0.81%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>232.5</v>
+        <v>248</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.87%1,169,000</t>
+          <t>0.90%1,107,336</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.90%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1169000</v>
+        <v>1107336</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.15%6845</t>
+          <t>0%232.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6845</v>
+        <v>232.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.86%39,000</t>
+          <t>0.89%1,169,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>39000</v>
+        <v>1169000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:41</t>
+          <t>2026-10-08 23:49:16</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+7.53%3140</t>
+          <t>-2.7%6660</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+7.53%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3140</v>
+        <v>6660</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.83%82,000</t>
+          <t>0.85%39,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>82000</v>
+        <v>39000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>7750新代</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.76%1995</t>
+          <t>-5.73%2960</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>-5.73%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1995</v>
+        <v>2960</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.78%122,000</t>
+          <t>0.79%82,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>122000</v>
+        <v>82000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,34 +2395,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>7750新代</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.56%252</t>
+          <t>-1%1975</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>252</v>
+        <v>1975</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.78%960,000</t>
+          <t>0.79%122,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>960000</v>
+        <v>122000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.24%4190</t>
+          <t>-1.19%249</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>4190</v>
+        <v>249</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.66%49,000</t>
+          <t>0.78%960,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>49000</v>
+        <v>960000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.95%497</t>
+          <t>0%497</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.54%340,000</t>
+          <t>0.55%340,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+7.05%250.5</t>
+          <t>-1%248</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+7.05%</t>
+          <t>-1%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>250.5</v>
+        <v>248</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3533嘉澤</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.14%1825</t>
+          <t>+1.89%188.5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>+1.89%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1825</v>
+        <v>188.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.45%77,000</t>
+          <t>0.51%819,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>77000</v>
+        <v>819000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5434崇越</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.26%605</t>
+          <t>+2.73%2070</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>+2.73%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>605</v>
+        <v>2070</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.39%200,000</t>
+          <t>0.50%74,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>200000</v>
+        <v>74000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3167大量</t>
+          <t>3533嘉澤</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.49%1025</t>
+          <t>+4.93%1915</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+4.93%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1025</v>
+        <v>1915</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.38%115,000</t>
+          <t>0.48%77,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>115000</v>
+        <v>77000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3293鈊象</t>
+          <t>3167大量</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0%780</t>
+          <t>+2.93%1055</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.93%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>780</v>
+        <v>1055</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.33%133,000</t>
+          <t>0.40%115,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>133000</v>
+        <v>115000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>5434崇越</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.58%174</t>
+          <t>-1.49%596</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>174</v>
+        <v>596</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.33%592,000</t>
+          <t>0.39%200,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>592000</v>
+        <v>200000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,34 +2944,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6271同欣電</t>
+          <t>3293鈊象</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.26%241.5</t>
+          <t>+1.03%788</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>+1.03%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>241.5</v>
+        <v>788</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.26%340,000</t>
+          <t>0.34%133,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>340000</v>
+        <v>133000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2637慧洋-KY</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-3.2%96.8</t>
+          <t>0%174</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>96.8</v>
+        <v>174</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.26%834,000</t>
+          <t>0.34%592,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>834000</v>
+        <v>592000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6121新普</t>
+          <t>6271同欣電</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.67%370</t>
+          <t>+1.66%245.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>+1.66%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>370</v>
+        <v>245.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.21%178,000</t>
+          <t>0.27%340,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>178000</v>
+        <v>340000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2637慧洋-KY</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.34%5885</t>
+          <t>+1.65%98.4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>+1.65%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5885</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.13%7,000</t>
+          <t>0.27%834,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>7000</v>
+        <v>834000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 00:28:42</t>
+          <t>2026-10-08 23:49:17</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,41 +3188,346 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>6121新普</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-1.62%364</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-1.62%</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>364</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0.21%178,000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.21%</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>178000</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-08 23:49:19</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>7769鴻勁</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>+0.68%5925</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>+0.68%</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>5925</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.14%7,000</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>7000</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-08 23:49:19</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>9939宏全</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>+0.79%127.5</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>+0.79%</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>127.5</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>0.07%180,000</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>+0.39%128</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>128</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.08%180,000</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>180000</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-08 23:49:19</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1476儒鴻</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>+4.38%310</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>+4.38%</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>310</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.07%70,000</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>0.07%</t>
         </is>
       </c>
-      <c r="K46" t="n">
-        <v>180000</v>
-      </c>
-      <c r="L46" t="inlineStr">
+      <c r="K49" t="n">
+        <v>70000</v>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>+0.00%</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-08 23:49:19</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1215卜蜂</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>+1.43%106.5</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>+1.43%</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.07%200,000</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.07%</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-08 23:49:19</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00400A/holdings</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2885元大金</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-2.43%68.3</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-2.43%</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.05%241,040</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>241040</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-08_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-08_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:15</t>
+          <t>2026-10-08 23:54:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:16</t>
+          <t>2026-10-08 23:54:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:17</t>
+          <t>2026-10-08 23:54:54</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:19</t>
+          <t>2026-10-08 23:54:55</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:19</t>
+          <t>2026-10-08 23:54:55</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:19</t>
+          <t>2026-10-08 23:54:55</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:19</t>
+          <t>2026-10-08 23:54:55</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-08 23:49:19</t>
+          <t>2026-10-08 23:54:55</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
